--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-29.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,6 +614,170 @@
       </c>
       <c r="T2" t="n">
         <v>38.98</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Romanian Cup</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FC Voluntari x Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FC Voluntari</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Spanish Copa del Rey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Pena Sport x Huesca</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Pena Sport</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="T4" t="n">
+        <v>30.81</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-29.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-29.xlsx
@@ -664,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.52</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -746,15 +750,19 @@
       <c r="K4" t="n">
         <v>1.55</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
